--- a/卒論データ.xlsx
+++ b/卒論データ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakamao/Desktop/ゼミ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B86DB9-8413-0546-BEBF-7F7A73CFDFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD375181-49DB-5E40-9634-D4E1C86C6CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="2040" windowWidth="23740" windowHeight="17360" activeTab="1" xr2:uid="{01908024-5782-E64F-93D1-6535529C0335}"/>
   </bookViews>
@@ -177,59 +177,38 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$18</c:f>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8</c:v>
+                  <c:v>1024</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>2048</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>64</c:v>
+                  <c:v>3500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>128</c:v>
+                  <c:v>3800</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>256</c:v>
+                  <c:v>3900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>512</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1024</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2048</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3500</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3800</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3900</c:v>
-                </c:pt>
-                <c:pt idx="16">
                   <c:v>4000</c:v>
                 </c:pt>
               </c:numCache>
@@ -237,59 +216,38 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$18</c:f>
+              <c:f>Sheet1!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>520</c:v>
+                  <c:v>588</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>688</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>528</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>496</c:v>
+                  <c:v>1336</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>1992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>496</c:v>
+                  <c:v>2804</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>612</c:v>
+                  <c:v>3084</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>604</c:v>
+                  <c:v>3344</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>660</c:v>
+                  <c:v>3368</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>708</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1336</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1992</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2804</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3084</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3344</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3368</c:v>
-                </c:pt>
-                <c:pt idx="16">
                   <c:v>1900</c:v>
                 </c:pt>
               </c:numCache>
@@ -1234,8 +1192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75582DDE-80E1-CD42-9E1D-DA070F96928F}" name="テーブル1" displayName="テーブル1" ref="A1:B18" totalsRowShown="0">
-  <autoFilter ref="A1:B18" xr:uid="{75582DDE-80E1-CD42-9E1D-DA070F96928F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75582DDE-80E1-CD42-9E1D-DA070F96928F}" name="テーブル1" displayName="テーブル1" ref="A1:B11" totalsRowShown="0">
+  <autoFilter ref="A1:B11" xr:uid="{75582DDE-80E1-CD42-9E1D-DA070F96928F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{D0F668BB-7549-404A-A988-92FA55835E6C}" name="同時接続数"/>
     <tableColumn id="2" xr3:uid="{C0CE7C55-3658-7E4C-ACD5-94D38065F81C}" name="メモリ消費量"/>
@@ -1571,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{665DF877-04FC-4D4E-B20A-A6DD466355F6}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -1587,137 +1545,81 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="B2">
-        <v>520</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="B3">
-        <v>500</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4</v>
+        <v>512</v>
       </c>
       <c r="B4">
-        <v>528</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>8</v>
+        <v>1024</v>
       </c>
       <c r="B5">
-        <v>496</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>16</v>
+        <v>2048</v>
       </c>
       <c r="B6">
-        <v>600</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>32</v>
+        <v>3000</v>
       </c>
       <c r="B7">
-        <v>496</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>64</v>
+        <v>3500</v>
       </c>
       <c r="B8">
-        <v>612</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>128</v>
+        <v>3800</v>
       </c>
       <c r="B9">
-        <v>604</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>256</v>
+        <v>3900</v>
       </c>
       <c r="B10">
-        <v>660</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>512</v>
+        <v>4000</v>
       </c>
       <c r="B11">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>1024</v>
-      </c>
-      <c r="B12">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>2048</v>
-      </c>
-      <c r="B13">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>3000</v>
-      </c>
-      <c r="B14">
-        <v>2804</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>3500</v>
-      </c>
-      <c r="B15">
-        <v>3084</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>3800</v>
-      </c>
-      <c r="B16">
-        <v>3344</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>3900</v>
-      </c>
-      <c r="B17">
-        <v>3368</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>4000</v>
-      </c>
-      <c r="B18">
         <v>1900</v>
       </c>
     </row>

--- a/卒論データ.xlsx
+++ b/卒論データ.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakamao/Desktop/ゼミ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD375181-49DB-5E40-9634-D4E1C86C6CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419E2610-4D59-4E49-89CB-F25471B4CAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="2040" windowWidth="23740" windowHeight="17360" activeTab="1" xr2:uid="{01908024-5782-E64F-93D1-6535529C0335}"/>
+    <workbookView xWindow="3640" yWindow="1360" windowWidth="23240" windowHeight="14580" xr2:uid="{01908024-5782-E64F-93D1-6535529C0335}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>メモリ消費量</t>
     <phoneticPr fontId="1"/>
@@ -52,12 +51,16 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>kB</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -70,6 +73,15 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF595959"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -96,9 +108,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -221,34 +236,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>588</c:v>
+                  <c:v>552</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>688</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1020</c:v>
+                  <c:v>856</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1336</c:v>
+                  <c:v>1204</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1992</c:v>
+                  <c:v>2044</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2804</c:v>
+                  <c:v>2812</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3084</c:v>
+                  <c:v>3132</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3344</c:v>
+                  <c:v>3328</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>3368</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1900</c:v>
+                  <c:v>3432</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -313,7 +328,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -326,7 +341,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1"/>
                   <a:t>同時接続数</a:t>
                 </a:r>
               </a:p>
@@ -345,7 +360,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -383,7 +398,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -446,13 +461,13 @@
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="eaVert" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:pPr lvl="1" algn="ctr" rtl="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
+                      <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65000"/>
                         <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      </a:sysClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -460,14 +475,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US" b="1"/>
+                  <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1"/>
                   <a:t>メモリ消費量</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP" b="1"/>
+                  <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="1"/>
                   <a:t>[kB]</a:t>
                 </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US" b="1"/>
+                <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1200" b="1"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -491,24 +506,24 @@
             <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="eaVert" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:pPr lvl="1" algn="ctr" rtl="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
+                    <a:sysClr val="windowText" lastClr="000000">
                       <a:lumMod val="65000"/>
                       <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    </a:sysClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -530,7 +545,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1518,24 +1533,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D41FC4D-578F-6D44-A627-5EFFF309EDA3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{665DF877-04FC-4D4E-B20A-A6DD466355F6}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1543,71 +1548,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>128</v>
       </c>
       <c r="B2">
-        <v>588</v>
+        <v>552</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>256</v>
       </c>
       <c r="B3">
         <v>688</v>
       </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>512</v>
       </c>
       <c r="B4">
-        <v>1020</v>
+        <v>856</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>1024</v>
       </c>
       <c r="B5">
-        <v>1336</v>
+        <v>1204</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>2048</v>
       </c>
       <c r="B6">
-        <v>1992</v>
+        <v>2044</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>3000</v>
       </c>
       <c r="B7">
-        <v>2804</v>
+        <v>2812</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>3500</v>
       </c>
       <c r="B8">
-        <v>3084</v>
+        <v>3132</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>3800</v>
       </c>
       <c r="B9">
-        <v>3344</v>
-      </c>
+        <v>3328</v>
+      </c>
+      <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>3900</v>
       </c>
@@ -1615,12 +1624,12 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>4000</v>
       </c>
       <c r="B11">
-        <v>1900</v>
+        <v>3432</v>
       </c>
     </row>
   </sheetData>

--- a/卒論データ.xlsx
+++ b/卒論データ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakamao/Desktop/ゼミ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419E2610-4D59-4E49-89CB-F25471B4CAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E436011-74FD-D747-B523-8EBF7DFD8E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1360" windowWidth="23240" windowHeight="14580" xr2:uid="{01908024-5782-E64F-93D1-6535529C0335}"/>
   </bookViews>
@@ -480,7 +480,7 @@
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="1"/>
-                  <a:t>[kB]</a:t>
+                  <a:t>[KB]</a:t>
                 </a:r>
                 <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1200" b="1"/>
               </a:p>
